--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/8423-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/8423-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5080C058-FDF1-43BD-81C9-E2CEC4ED3FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77054322-DAF2-4FA8-B6C7-4048754486FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{1C8DC7E4-11B1-4F00-894E-A832D1AAF472}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{2AA81D19-95FF-479A-895D-9D4835E5C6A2}"/>
   </bookViews>
   <sheets>
     <sheet name="8423-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1400,20 +1400,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB7F5B10-7D9D-411F-8FCF-BA6A5755951B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DAFBFBA-1841-49EF-ADDB-345A025E89A1}">
   <dimension ref="A1:R20"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="9" width="7.33203125" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="2" width="16.375" customWidth="1"/>
+    <col min="3" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1441,7 +1441,7 @@
       <c r="Q1" s="27"/>
       <c r="R1" s="19"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1471,7 +1471,7 @@
       <c r="Q2" s="29"/>
       <c r="R2" s="30"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1517,7 +1517,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1567,7 +1567,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="34">
         <v>2025</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="36">
         <v>2024</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="34">
         <v>2023</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="36">
         <v>2022</v>
       </c>
@@ -1783,7 +1783,7 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="34">
         <v>2021</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
         <v>2020</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>5.46</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="34">
         <v>2019</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="36">
         <v>2018</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="34">
         <v>2017</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>2016</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>4.21</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="34">
         <v>2015</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
         <v>2014</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="34">
         <v>2013</v>
       </c>
@@ -2269,7 +2269,7 @@
         <v>3.27</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>2012</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>1.63</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="34">
         <v>2011</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="36" t="s">
         <v>25</v>
       </c>
